--- a/excel-files/PASIG/PALATIW ELEMENTARY SCHOOL.xlsx
+++ b/excel-files/PASIG/PALATIW ELEMENTARY SCHOOL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29721"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29917"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="152" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A32D61FE-68E3-4A8C-B7AD-8107F9F1B311}"/>
+  <xr:revisionPtr revIDLastSave="350" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9A6733C4-7D59-4787-BEBC-E1C7A1BD5F3B}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TextBooks" sheetId="1" r:id="rId1"/>
@@ -14025,14 +14025,17 @@
         <v>3104</v>
       </c>
       <c r="I3" s="5">
-        <f t="shared" ref="I3:I83" si="1">IF((E3-D3)&lt;0,0,(E3-D3))</f>
+        <f t="shared" ref="I3:K83" si="1">IF((E3-D3)&lt;0,0,(E3-D3))</f>
         <v>0</v>
       </c>
       <c r="J3" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3104</v>
       </c>
-      <c r="K3" s="5"/>
+      <c r="K3" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="L3" s="1"/>
       <c r="M3" s="5"/>
       <c r="N3" s="5">
@@ -14047,7 +14050,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3104</v>
       </c>
-      <c r="Q3" s="5"/>
+      <c r="Q3" s="5">
+        <v>0</v>
+      </c>
       <c r="R3" s="1"/>
       <c r="S3" s="5"/>
       <c r="T3" s="5">
@@ -14062,7 +14067,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3104</v>
       </c>
-      <c r="W3" s="5"/>
+      <c r="W3" s="5">
+        <v>0</v>
+      </c>
       <c r="X3" s="1"/>
       <c r="Y3" s="5"/>
       <c r="Z3" s="5">
@@ -14103,7 +14110,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3104</v>
       </c>
-      <c r="K4" s="5"/>
+      <c r="K4" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="L4" s="1"/>
       <c r="M4" s="5"/>
       <c r="N4" s="5">
@@ -14118,7 +14128,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3104</v>
       </c>
-      <c r="Q4" s="5"/>
+      <c r="Q4" s="5">
+        <v>0</v>
+      </c>
       <c r="R4" s="1"/>
       <c r="S4" s="5"/>
       <c r="T4" s="5">
@@ -14133,7 +14145,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3104</v>
       </c>
-      <c r="W4" s="5"/>
+      <c r="W4" s="5">
+        <v>0</v>
+      </c>
       <c r="X4" s="1"/>
       <c r="Y4" s="5"/>
       <c r="Z4" s="5">
@@ -14174,7 +14188,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3104</v>
       </c>
-      <c r="K5" s="5"/>
+      <c r="K5" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="L5" s="1"/>
       <c r="M5" s="5"/>
       <c r="N5" s="5">
@@ -14189,7 +14206,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3104</v>
       </c>
-      <c r="Q5" s="5"/>
+      <c r="Q5" s="5">
+        <v>0</v>
+      </c>
       <c r="R5" s="1"/>
       <c r="S5" s="5"/>
       <c r="T5" s="5">
@@ -14204,7 +14223,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3104</v>
       </c>
-      <c r="W5" s="5"/>
+      <c r="W5" s="5">
+        <v>0</v>
+      </c>
       <c r="X5" s="1"/>
       <c r="Y5" s="5"/>
       <c r="Z5" s="5">
@@ -14245,7 +14266,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3104</v>
       </c>
-      <c r="K6" s="5"/>
+      <c r="K6" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="L6" s="1"/>
       <c r="M6" s="5"/>
       <c r="N6" s="5">
@@ -14260,7 +14284,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3104</v>
       </c>
-      <c r="Q6" s="5"/>
+      <c r="Q6" s="5">
+        <v>0</v>
+      </c>
       <c r="R6" s="1"/>
       <c r="S6" s="5"/>
       <c r="T6" s="5">
@@ -14275,7 +14301,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3104</v>
       </c>
-      <c r="W6" s="5"/>
+      <c r="W6" s="5">
+        <v>0</v>
+      </c>
       <c r="X6" s="1"/>
       <c r="Y6" s="5"/>
       <c r="Z6" s="5">
@@ -14316,7 +14344,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3104</v>
       </c>
-      <c r="K7" s="5"/>
+      <c r="K7" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="L7" s="1"/>
       <c r="M7" s="5"/>
       <c r="N7" s="5">
@@ -14331,7 +14362,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3104</v>
       </c>
-      <c r="Q7" s="5"/>
+      <c r="Q7" s="5">
+        <v>0</v>
+      </c>
       <c r="R7" s="1"/>
       <c r="S7" s="5"/>
       <c r="T7" s="5">
@@ -14346,7 +14379,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3104</v>
       </c>
-      <c r="W7" s="5"/>
+      <c r="W7" s="5">
+        <v>0</v>
+      </c>
       <c r="X7" s="1"/>
       <c r="Y7" s="5"/>
       <c r="Z7" s="5">
@@ -14387,7 +14422,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3104</v>
       </c>
-      <c r="K8" s="5"/>
+      <c r="K8" s="5">
+        <f>IF((G8-F8)&lt;0,0,(G8-F8))</f>
+        <v>0</v>
+      </c>
       <c r="L8" s="1"/>
       <c r="M8" s="5"/>
       <c r="N8" s="5">
@@ -14402,7 +14440,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3104</v>
       </c>
-      <c r="Q8" s="5"/>
+      <c r="Q8" s="5">
+        <v>0</v>
+      </c>
       <c r="R8" s="1"/>
       <c r="S8" s="5"/>
       <c r="T8" s="5">
@@ -14417,7 +14457,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3104</v>
       </c>
-      <c r="W8" s="5"/>
+      <c r="W8" s="5">
+        <v>0</v>
+      </c>
       <c r="X8" s="1"/>
       <c r="Y8" s="5"/>
       <c r="Z8" s="5">
@@ -14458,7 +14500,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3104</v>
       </c>
-      <c r="K9" s="5"/>
+      <c r="K9" s="5">
+        <f>IF((G9-F9)&lt;0,0,(G9-F9))</f>
+        <v>0</v>
+      </c>
       <c r="L9" s="1"/>
       <c r="M9" s="5"/>
       <c r="N9" s="5">
@@ -14473,7 +14518,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3104</v>
       </c>
-      <c r="Q9" s="5"/>
+      <c r="Q9" s="5">
+        <v>0</v>
+      </c>
       <c r="R9" s="1"/>
       <c r="S9" s="5"/>
       <c r="T9" s="5">
@@ -14488,7 +14535,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3104</v>
       </c>
-      <c r="W9" s="5"/>
+      <c r="W9" s="5">
+        <v>0</v>
+      </c>
       <c r="X9" s="1"/>
       <c r="Y9" s="5"/>
       <c r="Z9" s="5">
@@ -14529,7 +14578,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3104</v>
       </c>
-      <c r="K10" s="5"/>
+      <c r="K10" s="5">
+        <f>IF((G10-F10)&lt;0,0,(G10-F10))</f>
+        <v>0</v>
+      </c>
       <c r="L10" s="1"/>
       <c r="M10" s="5"/>
       <c r="N10" s="5">
@@ -14544,7 +14596,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3104</v>
       </c>
-      <c r="Q10" s="5"/>
+      <c r="Q10" s="5">
+        <v>0</v>
+      </c>
       <c r="R10" s="1"/>
       <c r="S10" s="5"/>
       <c r="T10" s="5">
@@ -14559,7 +14613,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3104</v>
       </c>
-      <c r="W10" s="5"/>
+      <c r="W10" s="5">
+        <v>0</v>
+      </c>
       <c r="X10" s="1"/>
       <c r="Y10" s="5"/>
       <c r="Z10" s="5">
@@ -14601,7 +14657,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3280</v>
       </c>
-      <c r="K12" s="5"/>
+      <c r="K12" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="L12" s="1"/>
       <c r="M12" s="5"/>
       <c r="N12" s="5">
@@ -14616,7 +14675,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3280</v>
       </c>
-      <c r="Q12" s="5"/>
+      <c r="Q12" s="5">
+        <v>0</v>
+      </c>
       <c r="R12" s="1"/>
       <c r="S12" s="5"/>
       <c r="T12" s="5">
@@ -14631,7 +14692,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3280</v>
       </c>
-      <c r="W12" s="5"/>
+      <c r="W12" s="5">
+        <v>0</v>
+      </c>
       <c r="X12" s="1"/>
       <c r="Y12" s="5"/>
       <c r="Z12" s="5">
@@ -14672,7 +14735,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3280</v>
       </c>
-      <c r="K13" s="5"/>
+      <c r="K13" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="L13" s="1"/>
       <c r="M13" s="5"/>
       <c r="N13" s="5">
@@ -14687,7 +14753,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3280</v>
       </c>
-      <c r="Q13" s="5"/>
+      <c r="Q13" s="5">
+        <v>0</v>
+      </c>
       <c r="R13" s="1"/>
       <c r="S13" s="5"/>
       <c r="T13" s="5">
@@ -14702,7 +14770,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3280</v>
       </c>
-      <c r="W13" s="5"/>
+      <c r="W13" s="5">
+        <v>0</v>
+      </c>
       <c r="X13" s="1"/>
       <c r="Y13" s="5"/>
       <c r="Z13" s="5">
@@ -14743,7 +14813,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3280</v>
       </c>
-      <c r="K14" s="5"/>
+      <c r="K14" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="L14" s="1"/>
       <c r="M14" s="5"/>
       <c r="N14" s="5">
@@ -14758,7 +14831,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3280</v>
       </c>
-      <c r="Q14" s="5"/>
+      <c r="Q14" s="5">
+        <v>0</v>
+      </c>
       <c r="R14" s="1"/>
       <c r="S14" s="5"/>
       <c r="T14" s="5">
@@ -14773,7 +14848,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3280</v>
       </c>
-      <c r="W14" s="5"/>
+      <c r="W14" s="5">
+        <v>0</v>
+      </c>
       <c r="X14" s="1"/>
       <c r="Y14" s="5"/>
       <c r="Z14" s="5">
@@ -14814,7 +14891,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3280</v>
       </c>
-      <c r="K15" s="5"/>
+      <c r="K15" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="L15" s="1"/>
       <c r="M15" s="5"/>
       <c r="N15" s="5">
@@ -14829,7 +14909,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3280</v>
       </c>
-      <c r="Q15" s="5"/>
+      <c r="Q15" s="5">
+        <v>0</v>
+      </c>
       <c r="R15" s="1"/>
       <c r="S15" s="5"/>
       <c r="T15" s="5">
@@ -14844,7 +14926,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3280</v>
       </c>
-      <c r="W15" s="5"/>
+      <c r="W15" s="5">
+        <v>0</v>
+      </c>
       <c r="X15" s="1"/>
       <c r="Y15" s="5"/>
       <c r="Z15" s="5">
@@ -14885,7 +14969,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3280</v>
       </c>
-      <c r="K16" s="5"/>
+      <c r="K16" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="L16" s="1"/>
       <c r="M16" s="5"/>
       <c r="N16" s="5">
@@ -14900,7 +14987,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3280</v>
       </c>
-      <c r="Q16" s="5"/>
+      <c r="Q16" s="5">
+        <v>0</v>
+      </c>
       <c r="R16" s="1"/>
       <c r="S16" s="5"/>
       <c r="T16" s="5">
@@ -14915,7 +15004,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3280</v>
       </c>
-      <c r="W16" s="5"/>
+      <c r="W16" s="5">
+        <v>0</v>
+      </c>
       <c r="X16" s="1"/>
       <c r="Y16" s="5"/>
       <c r="Z16" s="5">
@@ -14956,7 +15047,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3280</v>
       </c>
-      <c r="K17" s="5"/>
+      <c r="K17" s="5">
+        <f>IF((G17-F17)&lt;0,0,(G17-F17))</f>
+        <v>0</v>
+      </c>
       <c r="L17" s="1"/>
       <c r="M17" s="5"/>
       <c r="N17" s="5">
@@ -14971,7 +15065,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3280</v>
       </c>
-      <c r="Q17" s="5"/>
+      <c r="Q17" s="5">
+        <v>0</v>
+      </c>
       <c r="R17" s="1"/>
       <c r="S17" s="5"/>
       <c r="T17" s="5">
@@ -14986,7 +15082,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3280</v>
       </c>
-      <c r="W17" s="5"/>
+      <c r="W17" s="5">
+        <v>0</v>
+      </c>
       <c r="X17" s="1"/>
       <c r="Y17" s="5"/>
       <c r="Z17" s="5">
@@ -15027,7 +15125,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3280</v>
       </c>
-      <c r="K18" s="5"/>
+      <c r="K18" s="5">
+        <f>IF((G18-F18)&lt;0,0,(G18-F18))</f>
+        <v>0</v>
+      </c>
       <c r="L18" s="1"/>
       <c r="M18" s="5"/>
       <c r="N18" s="5">
@@ -15042,7 +15143,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3280</v>
       </c>
-      <c r="Q18" s="5"/>
+      <c r="Q18" s="5">
+        <v>0</v>
+      </c>
       <c r="R18" s="1"/>
       <c r="S18" s="5"/>
       <c r="T18" s="5">
@@ -15057,7 +15160,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3280</v>
       </c>
-      <c r="W18" s="5"/>
+      <c r="W18" s="5">
+        <v>0</v>
+      </c>
       <c r="X18" s="1"/>
       <c r="Y18" s="5"/>
       <c r="Z18" s="5">
@@ -15098,7 +15203,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3280</v>
       </c>
-      <c r="K19" s="5"/>
+      <c r="K19" s="5">
+        <f>IF((G19-F19)&lt;0,0,(G19-F19))</f>
+        <v>0</v>
+      </c>
       <c r="L19" s="1"/>
       <c r="M19" s="5"/>
       <c r="N19" s="5">
@@ -15113,7 +15221,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3280</v>
       </c>
-      <c r="Q19" s="5"/>
+      <c r="Q19" s="5">
+        <v>0</v>
+      </c>
       <c r="R19" s="1"/>
       <c r="S19" s="5"/>
       <c r="T19" s="5">
@@ -15128,7 +15238,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3280</v>
       </c>
-      <c r="W19" s="5"/>
+      <c r="W19" s="5">
+        <v>0</v>
+      </c>
       <c r="X19" s="1"/>
       <c r="Y19" s="5"/>
       <c r="Z19" s="5">
@@ -15170,7 +15282,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3080</v>
       </c>
-      <c r="K21" s="5"/>
+      <c r="K21" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="L21" s="1"/>
       <c r="M21" s="5"/>
       <c r="N21" s="5">
@@ -15185,7 +15300,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3080</v>
       </c>
-      <c r="Q21" s="5"/>
+      <c r="Q21" s="5">
+        <v>0</v>
+      </c>
       <c r="R21" s="1"/>
       <c r="S21" s="5"/>
       <c r="T21" s="5">
@@ -15200,7 +15317,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3080</v>
       </c>
-      <c r="W21" s="5"/>
+      <c r="W21" s="5">
+        <v>0</v>
+      </c>
       <c r="X21" s="1"/>
       <c r="Y21" s="5"/>
       <c r="Z21" s="5">
@@ -15241,7 +15360,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3080</v>
       </c>
-      <c r="K22" s="5"/>
+      <c r="K22" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="L22" s="1"/>
       <c r="M22" s="5"/>
       <c r="N22" s="5">
@@ -15256,7 +15378,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3080</v>
       </c>
-      <c r="Q22" s="5"/>
+      <c r="Q22" s="5">
+        <v>0</v>
+      </c>
       <c r="R22" s="1"/>
       <c r="S22" s="5"/>
       <c r="T22" s="5">
@@ -15271,7 +15395,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3080</v>
       </c>
-      <c r="W22" s="5"/>
+      <c r="W22" s="5">
+        <v>0</v>
+      </c>
       <c r="X22" s="1"/>
       <c r="Y22" s="5"/>
       <c r="Z22" s="5">
@@ -15312,7 +15438,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3080</v>
       </c>
-      <c r="K23" s="5"/>
+      <c r="K23" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="L23" s="1"/>
       <c r="M23" s="5"/>
       <c r="N23" s="5">
@@ -15327,7 +15456,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3080</v>
       </c>
-      <c r="Q23" s="5"/>
+      <c r="Q23" s="5">
+        <v>0</v>
+      </c>
       <c r="R23" s="1"/>
       <c r="S23" s="5"/>
       <c r="T23" s="5">
@@ -15342,7 +15473,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3080</v>
       </c>
-      <c r="W23" s="5"/>
+      <c r="W23" s="5">
+        <v>0</v>
+      </c>
       <c r="X23" s="1"/>
       <c r="Y23" s="5"/>
       <c r="Z23" s="5">
@@ -15383,7 +15516,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3080</v>
       </c>
-      <c r="K24" s="5"/>
+      <c r="K24" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="L24" s="1"/>
       <c r="M24" s="5"/>
       <c r="N24" s="5">
@@ -15398,7 +15534,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3080</v>
       </c>
-      <c r="Q24" s="5"/>
+      <c r="Q24" s="5">
+        <v>0</v>
+      </c>
       <c r="R24" s="1"/>
       <c r="S24" s="5"/>
       <c r="T24" s="5">
@@ -15413,7 +15551,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3080</v>
       </c>
-      <c r="W24" s="5"/>
+      <c r="W24" s="5">
+        <v>0</v>
+      </c>
       <c r="X24" s="1"/>
       <c r="Y24" s="5"/>
       <c r="Z24" s="5">
@@ -15454,7 +15594,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3080</v>
       </c>
-      <c r="K25" s="5"/>
+      <c r="K25" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="L25" s="1"/>
       <c r="M25" s="5"/>
       <c r="N25" s="5">
@@ -15469,7 +15612,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3080</v>
       </c>
-      <c r="Q25" s="5"/>
+      <c r="Q25" s="5">
+        <v>0</v>
+      </c>
       <c r="R25" s="1"/>
       <c r="S25" s="5"/>
       <c r="T25" s="5">
@@ -15484,7 +15629,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3080</v>
       </c>
-      <c r="W25" s="5"/>
+      <c r="W25" s="5">
+        <v>0</v>
+      </c>
       <c r="X25" s="1"/>
       <c r="Y25" s="5"/>
       <c r="Z25" s="5">
@@ -15525,7 +15672,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3080</v>
       </c>
-      <c r="K26" s="5"/>
+      <c r="K26" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="L26" s="1"/>
       <c r="M26" s="5"/>
       <c r="N26" s="5">
@@ -15540,7 +15690,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3080</v>
       </c>
-      <c r="Q26" s="5"/>
+      <c r="Q26" s="5">
+        <v>0</v>
+      </c>
       <c r="R26" s="1"/>
       <c r="S26" s="5"/>
       <c r="T26" s="5">
@@ -15555,7 +15707,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3080</v>
       </c>
-      <c r="W26" s="5"/>
+      <c r="W26" s="5">
+        <v>0</v>
+      </c>
       <c r="X26" s="1"/>
       <c r="Y26" s="5"/>
       <c r="Z26" s="5">
@@ -15596,7 +15750,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3080</v>
       </c>
-      <c r="K27" s="5"/>
+      <c r="K27" s="5">
+        <f>IF((G27-F27)&lt;0,0,(G27-F27))</f>
+        <v>0</v>
+      </c>
       <c r="L27" s="1"/>
       <c r="M27" s="5"/>
       <c r="N27" s="5">
@@ -15611,7 +15768,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3080</v>
       </c>
-      <c r="Q27" s="5"/>
+      <c r="Q27" s="5">
+        <v>0</v>
+      </c>
       <c r="R27" s="1"/>
       <c r="S27" s="5"/>
       <c r="T27" s="5">
@@ -15626,7 +15785,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3080</v>
       </c>
-      <c r="W27" s="5"/>
+      <c r="W27" s="5">
+        <v>0</v>
+      </c>
       <c r="X27" s="1"/>
       <c r="Y27" s="5"/>
       <c r="Z27" s="5">
@@ -15667,7 +15828,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3080</v>
       </c>
-      <c r="K28" s="5"/>
+      <c r="K28" s="5">
+        <f>IF((G28-F28)&lt;0,0,(G28-F28))</f>
+        <v>0</v>
+      </c>
       <c r="L28" s="1"/>
       <c r="M28" s="5"/>
       <c r="N28" s="5">
@@ -15682,7 +15846,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3080</v>
       </c>
-      <c r="Q28" s="5"/>
+      <c r="Q28" s="5">
+        <v>0</v>
+      </c>
       <c r="R28" s="1"/>
       <c r="S28" s="5"/>
       <c r="T28" s="5">
@@ -15697,7 +15863,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3080</v>
       </c>
-      <c r="W28" s="5"/>
+      <c r="W28" s="5">
+        <v>0</v>
+      </c>
       <c r="X28" s="1"/>
       <c r="Y28" s="5"/>
       <c r="Z28" s="5">
@@ -15738,7 +15906,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3080</v>
       </c>
-      <c r="K29" s="5"/>
+      <c r="K29" s="5">
+        <f>IF((G29-F29)&lt;0,0,(G29-F29))</f>
+        <v>0</v>
+      </c>
       <c r="L29" s="1"/>
       <c r="M29" s="5"/>
       <c r="N29" s="5">
@@ -15753,7 +15924,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3080</v>
       </c>
-      <c r="Q29" s="5"/>
+      <c r="Q29" s="5">
+        <v>0</v>
+      </c>
       <c r="R29" s="1"/>
       <c r="S29" s="5"/>
       <c r="T29" s="5">
@@ -15768,7 +15941,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3080</v>
       </c>
-      <c r="W29" s="5"/>
+      <c r="W29" s="5">
+        <v>0</v>
+      </c>
       <c r="X29" s="1"/>
       <c r="Y29" s="5"/>
       <c r="Z29" s="5">
@@ -15810,7 +15985,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3640</v>
       </c>
-      <c r="K31" s="5"/>
+      <c r="K31" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="L31" s="1"/>
       <c r="M31" s="5"/>
       <c r="N31" s="5">
@@ -15825,7 +16003,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3640</v>
       </c>
-      <c r="Q31" s="5"/>
+      <c r="Q31" s="5">
+        <v>0</v>
+      </c>
       <c r="R31" s="1"/>
       <c r="S31" s="5"/>
       <c r="T31" s="5">
@@ -15840,7 +16020,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3640</v>
       </c>
-      <c r="W31" s="5"/>
+      <c r="W31" s="5">
+        <v>0</v>
+      </c>
       <c r="X31" s="1"/>
       <c r="Y31" s="5"/>
       <c r="Z31" s="5">
@@ -15881,7 +16063,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3640</v>
       </c>
-      <c r="K32" s="5"/>
+      <c r="K32" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="L32" s="1"/>
       <c r="M32" s="5"/>
       <c r="N32" s="5">
@@ -15896,7 +16081,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3640</v>
       </c>
-      <c r="Q32" s="5"/>
+      <c r="Q32" s="5">
+        <v>0</v>
+      </c>
       <c r="R32" s="1"/>
       <c r="S32" s="5"/>
       <c r="T32" s="5">
@@ -15911,7 +16098,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3640</v>
       </c>
-      <c r="W32" s="5"/>
+      <c r="W32" s="5">
+        <v>0</v>
+      </c>
       <c r="X32" s="1"/>
       <c r="Y32" s="5"/>
       <c r="Z32" s="5">
@@ -15952,7 +16141,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3640</v>
       </c>
-      <c r="K33" s="5"/>
+      <c r="K33" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="L33" s="1"/>
       <c r="M33" s="5"/>
       <c r="N33" s="5">
@@ -15967,7 +16159,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3640</v>
       </c>
-      <c r="Q33" s="5"/>
+      <c r="Q33" s="5">
+        <v>0</v>
+      </c>
       <c r="R33" s="1"/>
       <c r="S33" s="5"/>
       <c r="T33" s="5">
@@ -15982,7 +16176,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3640</v>
       </c>
-      <c r="W33" s="5"/>
+      <c r="W33" s="5">
+        <v>0</v>
+      </c>
       <c r="X33" s="1"/>
       <c r="Y33" s="5"/>
       <c r="Z33" s="5">
@@ -16023,7 +16219,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3640</v>
       </c>
-      <c r="K34" s="5"/>
+      <c r="K34" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="L34" s="1"/>
       <c r="M34" s="5"/>
       <c r="N34" s="5">
@@ -16038,7 +16237,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3640</v>
       </c>
-      <c r="Q34" s="5"/>
+      <c r="Q34" s="5">
+        <v>0</v>
+      </c>
       <c r="R34" s="1"/>
       <c r="S34" s="5"/>
       <c r="T34" s="5">
@@ -16053,7 +16254,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3640</v>
       </c>
-      <c r="W34" s="5"/>
+      <c r="W34" s="5">
+        <v>0</v>
+      </c>
       <c r="X34" s="1"/>
       <c r="Y34" s="5"/>
       <c r="Z34" s="5">
@@ -16094,7 +16297,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3640</v>
       </c>
-      <c r="K35" s="5"/>
+      <c r="K35" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="L35" s="1"/>
       <c r="M35" s="5"/>
       <c r="N35" s="5">
@@ -16109,7 +16315,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3640</v>
       </c>
-      <c r="Q35" s="5"/>
+      <c r="Q35" s="5">
+        <v>0</v>
+      </c>
       <c r="R35" s="1"/>
       <c r="S35" s="5"/>
       <c r="T35" s="5">
@@ -16124,7 +16332,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3640</v>
       </c>
-      <c r="W35" s="5"/>
+      <c r="W35" s="5">
+        <v>0</v>
+      </c>
       <c r="X35" s="1"/>
       <c r="Y35" s="5"/>
       <c r="Z35" s="5">
@@ -16165,7 +16375,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3640</v>
       </c>
-      <c r="K36" s="5"/>
+      <c r="K36" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="L36" s="1"/>
       <c r="M36" s="5"/>
       <c r="N36" s="5">
@@ -16180,7 +16393,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3640</v>
       </c>
-      <c r="Q36" s="5"/>
+      <c r="Q36" s="5">
+        <v>0</v>
+      </c>
       <c r="R36" s="1"/>
       <c r="S36" s="5"/>
       <c r="T36" s="5">
@@ -16195,7 +16410,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3640</v>
       </c>
-      <c r="W36" s="5"/>
+      <c r="W36" s="5">
+        <v>0</v>
+      </c>
       <c r="X36" s="1"/>
       <c r="Y36" s="5"/>
       <c r="Z36" s="5">
@@ -16236,7 +16453,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3640</v>
       </c>
-      <c r="K37" s="5"/>
+      <c r="K37" s="5">
+        <f>IF((G37-F37)&lt;0,0,(G37-F37))</f>
+        <v>0</v>
+      </c>
       <c r="L37" s="1"/>
       <c r="M37" s="5"/>
       <c r="N37" s="5">
@@ -16251,7 +16471,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3640</v>
       </c>
-      <c r="Q37" s="5"/>
+      <c r="Q37" s="5">
+        <v>0</v>
+      </c>
       <c r="R37" s="1"/>
       <c r="S37" s="5"/>
       <c r="T37" s="5">
@@ -16266,7 +16488,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3640</v>
       </c>
-      <c r="W37" s="5"/>
+      <c r="W37" s="5">
+        <v>0</v>
+      </c>
       <c r="X37" s="1"/>
       <c r="Y37" s="5"/>
       <c r="Z37" s="5">
@@ -16307,7 +16531,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3640</v>
       </c>
-      <c r="K38" s="5"/>
+      <c r="K38" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="L38" s="1"/>
       <c r="M38" s="5"/>
       <c r="N38" s="5">
@@ -16322,7 +16549,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3640</v>
       </c>
-      <c r="Q38" s="5"/>
+      <c r="Q38" s="5">
+        <v>0</v>
+      </c>
       <c r="R38" s="1"/>
       <c r="S38" s="5"/>
       <c r="T38" s="5">
@@ -16337,7 +16566,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3640</v>
       </c>
-      <c r="W38" s="5"/>
+      <c r="W38" s="5">
+        <v>0</v>
+      </c>
       <c r="X38" s="1"/>
       <c r="Y38" s="5"/>
       <c r="Z38" s="5">
@@ -16378,7 +16609,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3640</v>
       </c>
-      <c r="K39" s="5"/>
+      <c r="K39" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="L39" s="1"/>
       <c r="M39" s="5"/>
       <c r="N39" s="5">
@@ -16393,7 +16627,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3640</v>
       </c>
-      <c r="Q39" s="5"/>
+      <c r="Q39" s="5">
+        <v>0</v>
+      </c>
       <c r="R39" s="1"/>
       <c r="S39" s="5"/>
       <c r="T39" s="5">
@@ -16408,7 +16644,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3640</v>
       </c>
-      <c r="W39" s="5"/>
+      <c r="W39" s="5">
+        <v>0</v>
+      </c>
       <c r="X39" s="1"/>
       <c r="Y39" s="5"/>
       <c r="Z39" s="5">
@@ -16449,7 +16687,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3640</v>
       </c>
-      <c r="K40" s="5"/>
+      <c r="K40" s="5">
+        <f>IF((G40-F40)&lt;0,0,(G40-F40))</f>
+        <v>0</v>
+      </c>
       <c r="L40" s="1"/>
       <c r="M40" s="5"/>
       <c r="N40" s="5">
@@ -16464,7 +16705,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3640</v>
       </c>
-      <c r="Q40" s="5"/>
+      <c r="Q40" s="5">
+        <v>0</v>
+      </c>
       <c r="R40" s="1"/>
       <c r="S40" s="5"/>
       <c r="T40" s="5">
@@ -16479,7 +16722,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3640</v>
       </c>
-      <c r="W40" s="5"/>
+      <c r="W40" s="5">
+        <v>0</v>
+      </c>
       <c r="X40" s="1"/>
       <c r="Y40" s="5"/>
       <c r="Z40" s="5">
@@ -16520,7 +16765,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3640</v>
       </c>
-      <c r="K41" s="5"/>
+      <c r="K41" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="L41" s="1"/>
       <c r="M41" s="5"/>
       <c r="N41" s="5">
@@ -16535,7 +16783,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3640</v>
       </c>
-      <c r="Q41" s="5"/>
+      <c r="Q41" s="5">
+        <v>0</v>
+      </c>
       <c r="R41" s="1"/>
       <c r="S41" s="5"/>
       <c r="T41" s="5">
@@ -16550,7 +16800,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3640</v>
       </c>
-      <c r="W41" s="5"/>
+      <c r="W41" s="5">
+        <v>0</v>
+      </c>
       <c r="X41" s="1"/>
       <c r="Y41" s="5"/>
       <c r="Z41" s="5">
@@ -16592,7 +16844,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2984</v>
       </c>
-      <c r="K43" s="5"/>
+      <c r="K43" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="L43" s="1"/>
       <c r="M43" s="5"/>
       <c r="N43" s="5">
@@ -16607,7 +16862,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2984</v>
       </c>
-      <c r="Q43" s="5"/>
+      <c r="Q43" s="5">
+        <v>0</v>
+      </c>
       <c r="R43" s="1"/>
       <c r="S43" s="5"/>
       <c r="T43" s="5">
@@ -16622,7 +16879,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2984</v>
       </c>
-      <c r="W43" s="5"/>
+      <c r="W43" s="5">
+        <v>0</v>
+      </c>
       <c r="X43" s="1"/>
       <c r="Y43" s="5"/>
       <c r="Z43" s="5">
@@ -16663,7 +16922,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2984</v>
       </c>
-      <c r="K44" s="5"/>
+      <c r="K44" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="L44" s="1"/>
       <c r="M44" s="5"/>
       <c r="N44" s="5">
@@ -16678,7 +16940,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2984</v>
       </c>
-      <c r="Q44" s="5"/>
+      <c r="Q44" s="5">
+        <v>0</v>
+      </c>
       <c r="R44" s="1"/>
       <c r="S44" s="5"/>
       <c r="T44" s="5">
@@ -16693,7 +16957,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2984</v>
       </c>
-      <c r="W44" s="5"/>
+      <c r="W44" s="5">
+        <v>0</v>
+      </c>
       <c r="X44" s="1"/>
       <c r="Y44" s="5"/>
       <c r="Z44" s="5">
@@ -16734,7 +17000,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2984</v>
       </c>
-      <c r="K45" s="5"/>
+      <c r="K45" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="L45" s="1"/>
       <c r="M45" s="5"/>
       <c r="N45" s="5">
@@ -16749,7 +17018,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2984</v>
       </c>
-      <c r="Q45" s="5"/>
+      <c r="Q45" s="5">
+        <v>0</v>
+      </c>
       <c r="R45" s="1"/>
       <c r="S45" s="5"/>
       <c r="T45" s="5">
@@ -16764,7 +17035,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2984</v>
       </c>
-      <c r="W45" s="5"/>
+      <c r="W45" s="5">
+        <v>0</v>
+      </c>
       <c r="X45" s="1"/>
       <c r="Y45" s="5"/>
       <c r="Z45" s="5">
@@ -16805,7 +17078,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2984</v>
       </c>
-      <c r="K46" s="5"/>
+      <c r="K46" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="L46" s="1"/>
       <c r="M46" s="5"/>
       <c r="N46" s="5">
@@ -16820,7 +17096,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2984</v>
       </c>
-      <c r="Q46" s="5"/>
+      <c r="Q46" s="5">
+        <v>0</v>
+      </c>
       <c r="R46" s="1"/>
       <c r="S46" s="5"/>
       <c r="T46" s="5">
@@ -16835,7 +17113,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2984</v>
       </c>
-      <c r="W46" s="5"/>
+      <c r="W46" s="5">
+        <v>0</v>
+      </c>
       <c r="X46" s="1"/>
       <c r="Y46" s="5"/>
       <c r="Z46" s="5">
@@ -16876,7 +17156,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2984</v>
       </c>
-      <c r="K47" s="5"/>
+      <c r="K47" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="L47" s="1"/>
       <c r="M47" s="5"/>
       <c r="N47" s="5">
@@ -16891,7 +17174,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2984</v>
       </c>
-      <c r="Q47" s="5"/>
+      <c r="Q47" s="5">
+        <v>0</v>
+      </c>
       <c r="R47" s="1"/>
       <c r="S47" s="5"/>
       <c r="T47" s="5">
@@ -16906,7 +17191,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2984</v>
       </c>
-      <c r="W47" s="5"/>
+      <c r="W47" s="5">
+        <v>0</v>
+      </c>
       <c r="X47" s="1"/>
       <c r="Y47" s="5"/>
       <c r="Z47" s="5">
@@ -16947,7 +17234,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2984</v>
       </c>
-      <c r="K48" s="5"/>
+      <c r="K48" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="L48" s="1"/>
       <c r="M48" s="5"/>
       <c r="N48" s="5">
@@ -16962,7 +17252,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2984</v>
       </c>
-      <c r="Q48" s="5"/>
+      <c r="Q48" s="5">
+        <v>0</v>
+      </c>
       <c r="R48" s="1"/>
       <c r="S48" s="5"/>
       <c r="T48" s="5">
@@ -16977,7 +17269,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2984</v>
       </c>
-      <c r="W48" s="5"/>
+      <c r="W48" s="5">
+        <v>0</v>
+      </c>
       <c r="X48" s="1"/>
       <c r="Y48" s="5"/>
       <c r="Z48" s="5">
@@ -17018,7 +17312,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2984</v>
       </c>
-      <c r="K49" s="5"/>
+      <c r="K49" s="5">
+        <f>IF((G49-F49)&lt;0,0,(G49-F49))</f>
+        <v>0</v>
+      </c>
       <c r="L49" s="1"/>
       <c r="M49" s="5"/>
       <c r="N49" s="5">
@@ -17033,7 +17330,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2984</v>
       </c>
-      <c r="Q49" s="5"/>
+      <c r="Q49" s="5">
+        <v>0</v>
+      </c>
       <c r="R49" s="1"/>
       <c r="S49" s="5"/>
       <c r="T49" s="5">
@@ -17048,7 +17347,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2984</v>
       </c>
-      <c r="W49" s="5"/>
+      <c r="W49" s="5">
+        <v>0</v>
+      </c>
       <c r="X49" s="1"/>
       <c r="Y49" s="5"/>
       <c r="Z49" s="5">
@@ -17089,7 +17390,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2984</v>
       </c>
-      <c r="K50" s="5"/>
+      <c r="K50" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="L50" s="1"/>
       <c r="M50" s="5"/>
       <c r="N50" s="5">
@@ -17104,7 +17408,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2984</v>
       </c>
-      <c r="Q50" s="5"/>
+      <c r="Q50" s="5">
+        <v>0</v>
+      </c>
       <c r="R50" s="1"/>
       <c r="S50" s="5"/>
       <c r="T50" s="5">
@@ -17119,7 +17425,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2984</v>
       </c>
-      <c r="W50" s="5"/>
+      <c r="W50" s="5">
+        <v>0</v>
+      </c>
       <c r="X50" s="1"/>
       <c r="Y50" s="5"/>
       <c r="Z50" s="5">
@@ -17160,7 +17468,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2984</v>
       </c>
-      <c r="K51" s="5"/>
+      <c r="K51" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="L51" s="1"/>
       <c r="M51" s="5"/>
       <c r="N51" s="5">
@@ -17175,7 +17486,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2984</v>
       </c>
-      <c r="Q51" s="5"/>
+      <c r="Q51" s="5">
+        <v>0</v>
+      </c>
       <c r="R51" s="1"/>
       <c r="S51" s="5"/>
       <c r="T51" s="5">
@@ -17190,7 +17503,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2984</v>
       </c>
-      <c r="W51" s="5"/>
+      <c r="W51" s="5">
+        <v>0</v>
+      </c>
       <c r="X51" s="1"/>
       <c r="Y51" s="5"/>
       <c r="Z51" s="5">
@@ -17231,7 +17546,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2984</v>
       </c>
-      <c r="K52" s="5"/>
+      <c r="K52" s="5">
+        <f>IF((G52-F52)&lt;0,0,(G52-F52))</f>
+        <v>0</v>
+      </c>
       <c r="L52" s="1"/>
       <c r="M52" s="5"/>
       <c r="N52" s="5">
@@ -17246,7 +17564,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2984</v>
       </c>
-      <c r="Q52" s="5"/>
+      <c r="Q52" s="5">
+        <v>0</v>
+      </c>
       <c r="R52" s="1"/>
       <c r="S52" s="5"/>
       <c r="T52" s="5">
@@ -17261,7 +17581,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2984</v>
       </c>
-      <c r="W52" s="5"/>
+      <c r="W52" s="5">
+        <v>0</v>
+      </c>
       <c r="X52" s="1"/>
       <c r="Y52" s="5"/>
       <c r="Z52" s="5">
@@ -17302,7 +17624,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2984</v>
       </c>
-      <c r="K53" s="5"/>
+      <c r="K53" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="L53" s="1"/>
       <c r="M53" s="5"/>
       <c r="N53" s="5">
@@ -17317,7 +17642,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2984</v>
       </c>
-      <c r="Q53" s="5"/>
+      <c r="Q53" s="5">
+        <v>0</v>
+      </c>
       <c r="R53" s="1"/>
       <c r="S53" s="5"/>
       <c r="T53" s="5">
@@ -17332,7 +17659,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2984</v>
       </c>
-      <c r="W53" s="5"/>
+      <c r="W53" s="5">
+        <v>0</v>
+      </c>
       <c r="X53" s="1"/>
       <c r="Y53" s="5"/>
       <c r="Z53" s="5">
@@ -17374,7 +17703,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3280</v>
       </c>
-      <c r="K55" s="5"/>
+      <c r="K55" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="L55" s="1"/>
       <c r="M55" s="5"/>
       <c r="N55" s="5">
@@ -17389,7 +17721,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3280</v>
       </c>
-      <c r="Q55" s="5"/>
+      <c r="Q55" s="5">
+        <v>0</v>
+      </c>
       <c r="R55" s="1"/>
       <c r="S55" s="5"/>
       <c r="T55" s="5">
@@ -17404,7 +17738,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3280</v>
       </c>
-      <c r="W55" s="5"/>
+      <c r="W55" s="5">
+        <v>0</v>
+      </c>
       <c r="X55" s="1"/>
       <c r="Y55" s="5"/>
       <c r="Z55" s="5">
@@ -17445,7 +17781,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3280</v>
       </c>
-      <c r="K56" s="5"/>
+      <c r="K56" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="L56" s="1"/>
       <c r="M56" s="5"/>
       <c r="N56" s="5">
@@ -17460,7 +17799,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3280</v>
       </c>
-      <c r="Q56" s="5"/>
+      <c r="Q56" s="5">
+        <v>0</v>
+      </c>
       <c r="R56" s="1"/>
       <c r="S56" s="5"/>
       <c r="T56" s="5">
@@ -17475,7 +17816,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3280</v>
       </c>
-      <c r="W56" s="5"/>
+      <c r="W56" s="5">
+        <v>0</v>
+      </c>
       <c r="X56" s="1"/>
       <c r="Y56" s="5"/>
       <c r="Z56" s="5">
@@ -17516,7 +17859,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3280</v>
       </c>
-      <c r="K57" s="5"/>
+      <c r="K57" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="L57" s="1"/>
       <c r="M57" s="5"/>
       <c r="N57" s="5">
@@ -17531,7 +17877,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3280</v>
       </c>
-      <c r="Q57" s="5"/>
+      <c r="Q57" s="5">
+        <v>0</v>
+      </c>
       <c r="R57" s="1"/>
       <c r="S57" s="5"/>
       <c r="T57" s="5">
@@ -17546,7 +17894,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3280</v>
       </c>
-      <c r="W57" s="5"/>
+      <c r="W57" s="5">
+        <v>0</v>
+      </c>
       <c r="X57" s="1"/>
       <c r="Y57" s="5"/>
       <c r="Z57" s="5">
@@ -17587,7 +17937,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3280</v>
       </c>
-      <c r="K58" s="5"/>
+      <c r="K58" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="L58" s="1"/>
       <c r="M58" s="5"/>
       <c r="N58" s="5">
@@ -17602,7 +17955,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3280</v>
       </c>
-      <c r="Q58" s="5"/>
+      <c r="Q58" s="5">
+        <v>0</v>
+      </c>
       <c r="R58" s="1"/>
       <c r="S58" s="5"/>
       <c r="T58" s="5">
@@ -17617,7 +17972,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3280</v>
       </c>
-      <c r="W58" s="5"/>
+      <c r="W58" s="5">
+        <v>0</v>
+      </c>
       <c r="X58" s="1"/>
       <c r="Y58" s="5"/>
       <c r="Z58" s="5">
@@ -17658,7 +18015,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3280</v>
       </c>
-      <c r="K59" s="5"/>
+      <c r="K59" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="L59" s="1"/>
       <c r="M59" s="5"/>
       <c r="N59" s="5">
@@ -17673,7 +18033,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3280</v>
       </c>
-      <c r="Q59" s="5"/>
+      <c r="Q59" s="5">
+        <v>0</v>
+      </c>
       <c r="R59" s="1"/>
       <c r="S59" s="5"/>
       <c r="T59" s="5">
@@ -17688,7 +18050,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3280</v>
       </c>
-      <c r="W59" s="5"/>
+      <c r="W59" s="5">
+        <v>0</v>
+      </c>
       <c r="X59" s="1"/>
       <c r="Y59" s="5"/>
       <c r="Z59" s="5">
@@ -17729,7 +18093,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3280</v>
       </c>
-      <c r="K60" s="5"/>
+      <c r="K60" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="L60" s="1"/>
       <c r="M60" s="5"/>
       <c r="N60" s="5">
@@ -17744,7 +18111,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3280</v>
       </c>
-      <c r="Q60" s="5"/>
+      <c r="Q60" s="5">
+        <v>0</v>
+      </c>
       <c r="R60" s="1"/>
       <c r="S60" s="5"/>
       <c r="T60" s="5">
@@ -17759,7 +18128,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3280</v>
       </c>
-      <c r="W60" s="5"/>
+      <c r="W60" s="5">
+        <v>0</v>
+      </c>
       <c r="X60" s="1"/>
       <c r="Y60" s="5"/>
       <c r="Z60" s="5">
@@ -17800,7 +18171,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3280</v>
       </c>
-      <c r="K61" s="5"/>
+      <c r="K61" s="5">
+        <f>IF((G61-F61)&lt;0,0,(G61-F61))</f>
+        <v>0</v>
+      </c>
       <c r="L61" s="1"/>
       <c r="M61" s="5"/>
       <c r="N61" s="5">
@@ -17815,7 +18189,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3280</v>
       </c>
-      <c r="Q61" s="5"/>
+      <c r="Q61" s="5">
+        <v>0</v>
+      </c>
       <c r="R61" s="1"/>
       <c r="S61" s="5"/>
       <c r="T61" s="5">
@@ -17830,7 +18206,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3280</v>
       </c>
-      <c r="W61" s="5"/>
+      <c r="W61" s="5">
+        <v>0</v>
+      </c>
       <c r="X61" s="1"/>
       <c r="Y61" s="5"/>
       <c r="Z61" s="5">
@@ -17871,7 +18249,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3280</v>
       </c>
-      <c r="K62" s="5"/>
+      <c r="K62" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="L62" s="1"/>
       <c r="M62" s="5"/>
       <c r="N62" s="5">
@@ -17886,7 +18267,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3280</v>
       </c>
-      <c r="Q62" s="5"/>
+      <c r="Q62" s="5">
+        <v>0</v>
+      </c>
       <c r="R62" s="1"/>
       <c r="S62" s="5"/>
       <c r="T62" s="5">
@@ -17901,7 +18284,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3280</v>
       </c>
-      <c r="W62" s="5"/>
+      <c r="W62" s="5">
+        <v>0</v>
+      </c>
       <c r="X62" s="1"/>
       <c r="Y62" s="5"/>
       <c r="Z62" s="5">
@@ -17942,7 +18327,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3280</v>
       </c>
-      <c r="K63" s="5"/>
+      <c r="K63" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="L63" s="1"/>
       <c r="M63" s="5"/>
       <c r="N63" s="5">
@@ -17957,7 +18345,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3280</v>
       </c>
-      <c r="Q63" s="5"/>
+      <c r="Q63" s="5">
+        <v>0</v>
+      </c>
       <c r="R63" s="1"/>
       <c r="S63" s="5"/>
       <c r="T63" s="5">
@@ -17972,7 +18362,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3280</v>
       </c>
-      <c r="W63" s="5"/>
+      <c r="W63" s="5">
+        <v>0</v>
+      </c>
       <c r="X63" s="1"/>
       <c r="Y63" s="5"/>
       <c r="Z63" s="5">
@@ -18013,7 +18405,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3280</v>
       </c>
-      <c r="K64" s="5"/>
+      <c r="K64" s="5">
+        <f>IF((G64-F64)&lt;0,0,(G64-F64))</f>
+        <v>0</v>
+      </c>
       <c r="L64" s="1"/>
       <c r="M64" s="5"/>
       <c r="N64" s="5">
@@ -18028,7 +18423,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3280</v>
       </c>
-      <c r="Q64" s="5"/>
+      <c r="Q64" s="5">
+        <v>0</v>
+      </c>
       <c r="R64" s="1"/>
       <c r="S64" s="5"/>
       <c r="T64" s="5">
@@ -18043,7 +18440,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3280</v>
       </c>
-      <c r="W64" s="5"/>
+      <c r="W64" s="5">
+        <v>0</v>
+      </c>
       <c r="X64" s="1"/>
       <c r="Y64" s="5"/>
       <c r="Z64" s="5">
@@ -18084,7 +18483,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3280</v>
       </c>
-      <c r="K65" s="5"/>
+      <c r="K65" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="L65" s="1"/>
       <c r="M65" s="5"/>
       <c r="N65" s="5">
@@ -18099,7 +18501,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3280</v>
       </c>
-      <c r="Q65" s="5"/>
+      <c r="Q65" s="5">
+        <v>0</v>
+      </c>
       <c r="R65" s="1"/>
       <c r="S65" s="5"/>
       <c r="T65" s="5">
@@ -18114,7 +18518,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3280</v>
       </c>
-      <c r="W65" s="5"/>
+      <c r="W65" s="5">
+        <v>0</v>
+      </c>
       <c r="X65" s="1"/>
       <c r="Y65" s="5"/>
       <c r="Z65" s="5">
@@ -18127,7 +18533,7 @@
       </c>
     </row>
     <row r="66" spans="1:27" s="7" customFormat="1"/>
-    <row r="67" spans="1:27" ht="19.149999999999999">
+    <row r="67" spans="1:27" ht="19.5">
       <c r="A67" s="10">
         <v>7</v>
       </c>
@@ -18154,7 +18560,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="K67" s="12"/>
+      <c r="K67" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="L67" s="10"/>
       <c r="M67" s="12"/>
       <c r="N67" s="12">
@@ -18169,7 +18578,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="Q67" s="12"/>
+      <c r="Q67" s="12">
+        <v>0</v>
+      </c>
       <c r="R67" s="10"/>
       <c r="S67" s="12"/>
       <c r="T67" s="12">
@@ -18184,7 +18595,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="W67" s="12"/>
+      <c r="W67" s="12">
+        <v>0</v>
+      </c>
       <c r="X67" s="10"/>
       <c r="Y67" s="12"/>
       <c r="Z67" s="12">
@@ -18196,7 +18609,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:27" ht="19.149999999999999">
+    <row r="68" spans="1:27" ht="19.5">
       <c r="A68" s="10">
         <v>7</v>
       </c>
@@ -18223,7 +18636,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="K68" s="12"/>
+      <c r="K68" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="L68" s="10"/>
       <c r="M68" s="12"/>
       <c r="N68" s="12">
@@ -18238,7 +18654,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="Q68" s="12"/>
+      <c r="Q68" s="12">
+        <v>0</v>
+      </c>
       <c r="R68" s="10"/>
       <c r="S68" s="12"/>
       <c r="T68" s="12">
@@ -18253,7 +18671,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="W68" s="12"/>
+      <c r="W68" s="12">
+        <v>0</v>
+      </c>
       <c r="X68" s="10"/>
       <c r="Y68" s="12"/>
       <c r="Z68" s="12">
@@ -18265,7 +18685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:27" ht="19.149999999999999">
+    <row r="69" spans="1:27" ht="19.5">
       <c r="A69" s="10">
         <v>7</v>
       </c>
@@ -18292,7 +18712,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="K69" s="12"/>
+      <c r="K69" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="L69" s="10"/>
       <c r="M69" s="12"/>
       <c r="N69" s="12">
@@ -18307,7 +18730,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="Q69" s="12"/>
+      <c r="Q69" s="12">
+        <v>0</v>
+      </c>
       <c r="R69" s="10"/>
       <c r="S69" s="12"/>
       <c r="T69" s="12">
@@ -18322,7 +18747,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="W69" s="12"/>
+      <c r="W69" s="12">
+        <v>0</v>
+      </c>
       <c r="X69" s="10"/>
       <c r="Y69" s="12"/>
       <c r="Z69" s="12">
@@ -18334,7 +18761,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:27" ht="19.149999999999999">
+    <row r="70" spans="1:27" ht="19.5">
       <c r="A70" s="10">
         <v>7</v>
       </c>
@@ -18361,7 +18788,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="K70" s="12"/>
+      <c r="K70" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="L70" s="10"/>
       <c r="M70" s="12"/>
       <c r="N70" s="12">
@@ -18376,7 +18806,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="Q70" s="12"/>
+      <c r="Q70" s="12">
+        <v>0</v>
+      </c>
       <c r="R70" s="10"/>
       <c r="S70" s="12"/>
       <c r="T70" s="12">
@@ -18391,7 +18823,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="W70" s="12"/>
+      <c r="W70" s="12">
+        <v>0</v>
+      </c>
       <c r="X70" s="10"/>
       <c r="Y70" s="12"/>
       <c r="Z70" s="12">
@@ -18403,7 +18837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:27" ht="19.149999999999999">
+    <row r="71" spans="1:27" ht="38.25">
       <c r="A71" s="10">
         <v>7</v>
       </c>
@@ -18430,7 +18864,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="K71" s="12"/>
+      <c r="K71" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="L71" s="10"/>
       <c r="M71" s="12"/>
       <c r="N71" s="12">
@@ -18445,7 +18882,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="Q71" s="12"/>
+      <c r="Q71" s="12">
+        <v>0</v>
+      </c>
       <c r="R71" s="10"/>
       <c r="S71" s="12"/>
       <c r="T71" s="12">
@@ -18460,7 +18899,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="W71" s="12"/>
+      <c r="W71" s="12">
+        <v>0</v>
+      </c>
       <c r="X71" s="10"/>
       <c r="Y71" s="12"/>
       <c r="Z71" s="12">
@@ -18472,7 +18913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:27" ht="19.149999999999999">
+    <row r="72" spans="1:27" ht="19.5">
       <c r="A72" s="10">
         <v>7</v>
       </c>
@@ -18499,7 +18940,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="K72" s="12"/>
+      <c r="K72" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="L72" s="10"/>
       <c r="M72" s="12"/>
       <c r="N72" s="12">
@@ -18514,7 +18958,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="Q72" s="12"/>
+      <c r="Q72" s="12">
+        <v>0</v>
+      </c>
       <c r="R72" s="10"/>
       <c r="S72" s="12"/>
       <c r="T72" s="12">
@@ -18529,7 +18975,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="W72" s="12"/>
+      <c r="W72" s="12">
+        <v>0</v>
+      </c>
       <c r="X72" s="10"/>
       <c r="Y72" s="12"/>
       <c r="Z72" s="12">
@@ -18541,7 +18989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:27" ht="19.149999999999999">
+    <row r="73" spans="1:27" ht="19.5">
       <c r="A73" s="38">
         <v>7</v>
       </c>
@@ -18568,7 +19016,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="K73" s="12"/>
+      <c r="K73" s="12">
+        <f>IF((G73-F73)&lt;0,0,(G73-F73))</f>
+        <v>0</v>
+      </c>
       <c r="L73" s="10"/>
       <c r="M73" s="12"/>
       <c r="N73" s="12">
@@ -18583,7 +19034,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="Q73" s="12"/>
+      <c r="Q73" s="12">
+        <v>0</v>
+      </c>
       <c r="R73" s="10"/>
       <c r="S73" s="12"/>
       <c r="T73" s="12">
@@ -18598,7 +19051,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="W73" s="12"/>
+      <c r="W73" s="12">
+        <v>0</v>
+      </c>
       <c r="X73" s="10"/>
       <c r="Y73" s="12"/>
       <c r="Z73" s="12">
@@ -18610,7 +19065,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:27" ht="19.149999999999999">
+    <row r="74" spans="1:27" ht="19.5">
       <c r="A74" s="10">
         <v>7</v>
       </c>
@@ -18637,7 +19092,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="K74" s="12"/>
+      <c r="K74" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="L74" s="10"/>
       <c r="M74" s="12"/>
       <c r="N74" s="12">
@@ -18652,7 +19110,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="Q74" s="12"/>
+      <c r="Q74" s="12">
+        <v>0</v>
+      </c>
       <c r="R74" s="10"/>
       <c r="S74" s="12"/>
       <c r="T74" s="12">
@@ -18667,7 +19127,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="W74" s="12"/>
+      <c r="W74" s="12">
+        <v>0</v>
+      </c>
       <c r="X74" s="10"/>
       <c r="Y74" s="12"/>
       <c r="Z74" s="12">
@@ -18679,7 +19141,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:27" ht="19.149999999999999">
+    <row r="75" spans="1:27" ht="19.5">
       <c r="A75" s="10">
         <v>7</v>
       </c>
@@ -18706,7 +19168,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="K75" s="12"/>
+      <c r="K75" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="L75" s="10"/>
       <c r="M75" s="12"/>
       <c r="N75" s="12">
@@ -18721,7 +19186,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="Q75" s="12"/>
+      <c r="Q75" s="12">
+        <v>0</v>
+      </c>
       <c r="R75" s="10"/>
       <c r="S75" s="12"/>
       <c r="T75" s="12">
@@ -18736,7 +19203,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="W75" s="12"/>
+      <c r="W75" s="12">
+        <v>0</v>
+      </c>
       <c r="X75" s="10"/>
       <c r="Y75" s="12"/>
       <c r="Z75" s="12">
@@ -18748,7 +19217,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:27" ht="19.149999999999999">
+    <row r="76" spans="1:27" ht="19.5">
       <c r="A76" s="38">
         <v>7</v>
       </c>
@@ -18775,7 +19244,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="K76" s="12"/>
+      <c r="K76" s="12">
+        <f>IF((G76-F76)&lt;0,0,(G76-F76))</f>
+        <v>0</v>
+      </c>
       <c r="L76" s="10"/>
       <c r="M76" s="12"/>
       <c r="N76" s="12">
@@ -18790,7 +19262,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="Q76" s="12"/>
+      <c r="Q76" s="12">
+        <v>0</v>
+      </c>
       <c r="R76" s="10"/>
       <c r="S76" s="12"/>
       <c r="T76" s="12">
@@ -18805,7 +19279,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="W76" s="12"/>
+      <c r="W76" s="12">
+        <v>0</v>
+      </c>
       <c r="X76" s="10"/>
       <c r="Y76" s="12"/>
       <c r="Z76" s="12">
@@ -18817,7 +19293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:27" ht="19.149999999999999">
+    <row r="77" spans="1:27" ht="19.5">
       <c r="A77" s="10">
         <v>7</v>
       </c>
@@ -18844,7 +19320,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="K77" s="12"/>
+      <c r="K77" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="L77" s="10"/>
       <c r="M77" s="12"/>
       <c r="N77" s="12">
@@ -18859,7 +19338,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="Q77" s="12"/>
+      <c r="Q77" s="12">
+        <v>0</v>
+      </c>
       <c r="R77" s="10"/>
       <c r="S77" s="12"/>
       <c r="T77" s="12">
@@ -18874,7 +19355,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="W77" s="12"/>
+      <c r="W77" s="12">
+        <v>0</v>
+      </c>
       <c r="X77" s="10"/>
       <c r="Y77" s="12"/>
       <c r="Z77" s="12">
@@ -18887,7 +19370,7 @@
       </c>
     </row>
     <row r="78" spans="1:27" s="7" customFormat="1"/>
-    <row r="79" spans="1:27" ht="19.149999999999999">
+    <row r="79" spans="1:27" ht="19.5">
       <c r="A79" s="10">
         <v>8</v>
       </c>
@@ -18914,7 +19397,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="K79" s="12"/>
+      <c r="K79" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="L79" s="10"/>
       <c r="M79" s="12"/>
       <c r="N79" s="12">
@@ -18929,7 +19415,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="Q79" s="12"/>
+      <c r="Q79" s="12">
+        <v>0</v>
+      </c>
       <c r="R79" s="10"/>
       <c r="S79" s="12"/>
       <c r="T79" s="12">
@@ -18944,7 +19432,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="W79" s="12"/>
+      <c r="W79" s="12">
+        <v>0</v>
+      </c>
       <c r="X79" s="10"/>
       <c r="Y79" s="12"/>
       <c r="Z79" s="12">
@@ -18956,7 +19446,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:27" ht="19.149999999999999">
+    <row r="80" spans="1:27" ht="19.5">
       <c r="A80" s="10">
         <v>8</v>
       </c>
@@ -18983,7 +19473,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="K80" s="12"/>
+      <c r="K80" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="L80" s="10"/>
       <c r="M80" s="12"/>
       <c r="N80" s="12">
@@ -18998,7 +19491,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="Q80" s="12"/>
+      <c r="Q80" s="12">
+        <v>0</v>
+      </c>
       <c r="R80" s="10"/>
       <c r="S80" s="12"/>
       <c r="T80" s="12">
@@ -19013,7 +19508,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="W80" s="12"/>
+      <c r="W80" s="12">
+        <v>0</v>
+      </c>
       <c r="X80" s="10"/>
       <c r="Y80" s="12"/>
       <c r="Z80" s="12">
@@ -19025,7 +19522,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:27" ht="19.149999999999999">
+    <row r="81" spans="1:27" ht="19.5">
       <c r="A81" s="10">
         <v>8</v>
       </c>
@@ -19052,7 +19549,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="K81" s="12"/>
+      <c r="K81" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="L81" s="10"/>
       <c r="M81" s="12"/>
       <c r="N81" s="12">
@@ -19067,7 +19567,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="Q81" s="12"/>
+      <c r="Q81" s="12">
+        <v>0</v>
+      </c>
       <c r="R81" s="10"/>
       <c r="S81" s="12"/>
       <c r="T81" s="12">
@@ -19082,7 +19584,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="W81" s="12"/>
+      <c r="W81" s="12">
+        <v>0</v>
+      </c>
       <c r="X81" s="10"/>
       <c r="Y81" s="12"/>
       <c r="Z81" s="12">
@@ -19094,7 +19598,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:27" ht="19.149999999999999">
+    <row r="82" spans="1:27" ht="19.5">
       <c r="A82" s="10">
         <v>8</v>
       </c>
@@ -19121,7 +19625,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="K82" s="12"/>
+      <c r="K82" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="L82" s="10"/>
       <c r="M82" s="12"/>
       <c r="N82" s="12">
@@ -19136,7 +19643,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="Q82" s="12"/>
+      <c r="Q82" s="12">
+        <v>0</v>
+      </c>
       <c r="R82" s="10"/>
       <c r="S82" s="12"/>
       <c r="T82" s="12">
@@ -19151,7 +19660,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="W82" s="12"/>
+      <c r="W82" s="12">
+        <v>0</v>
+      </c>
       <c r="X82" s="10"/>
       <c r="Y82" s="12"/>
       <c r="Z82" s="12">
@@ -19163,7 +19674,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:27" ht="19.149999999999999">
+    <row r="83" spans="1:27" ht="19.5">
       <c r="A83" s="10">
         <v>8</v>
       </c>
@@ -19190,7 +19701,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="K83" s="12"/>
+      <c r="K83" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="L83" s="10"/>
       <c r="M83" s="12"/>
       <c r="N83" s="12">
@@ -19205,7 +19719,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="Q83" s="12"/>
+      <c r="Q83" s="12">
+        <v>0</v>
+      </c>
       <c r="R83" s="10"/>
       <c r="S83" s="12"/>
       <c r="T83" s="12">
@@ -19220,7 +19736,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="W83" s="12"/>
+      <c r="W83" s="12">
+        <v>0</v>
+      </c>
       <c r="X83" s="10"/>
       <c r="Y83" s="12"/>
       <c r="Z83" s="12">
@@ -19232,7 +19750,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:27" ht="19.149999999999999">
+    <row r="84" spans="1:27" ht="19.5">
       <c r="A84" s="10">
         <v>8</v>
       </c>
@@ -19252,14 +19770,17 @@
         <v>0</v>
       </c>
       <c r="I84" s="12">
-        <f t="shared" ref="I84:I122" si="23">IF((E84-D84)&lt;0,0,(E84-D84))</f>
+        <f t="shared" ref="I84:K122" si="23">IF((E84-D84)&lt;0,0,(E84-D84))</f>
         <v>0</v>
       </c>
       <c r="J84" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="K84" s="12"/>
+      <c r="K84" s="12">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
       <c r="L84" s="10"/>
       <c r="M84" s="12"/>
       <c r="N84" s="12">
@@ -19274,7 +19795,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="Q84" s="12"/>
+      <c r="Q84" s="12">
+        <v>0</v>
+      </c>
       <c r="R84" s="10"/>
       <c r="S84" s="12"/>
       <c r="T84" s="12">
@@ -19289,7 +19812,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="W84" s="12"/>
+      <c r="W84" s="12">
+        <v>0</v>
+      </c>
       <c r="X84" s="10"/>
       <c r="Y84" s="12"/>
       <c r="Z84" s="12">
@@ -19301,7 +19826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:27" ht="19.149999999999999">
+    <row r="85" spans="1:27" ht="19.5">
       <c r="A85" s="38">
         <v>8</v>
       </c>
@@ -19328,7 +19853,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="K85" s="12"/>
+      <c r="K85" s="12">
+        <f>IF((G85-F85)&lt;0,0,(G85-F85))</f>
+        <v>0</v>
+      </c>
       <c r="L85" s="10"/>
       <c r="M85" s="12"/>
       <c r="N85" s="12">
@@ -19343,7 +19871,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="Q85" s="12"/>
+      <c r="Q85" s="12">
+        <v>0</v>
+      </c>
       <c r="R85" s="10"/>
       <c r="S85" s="12"/>
       <c r="T85" s="12">
@@ -19358,7 +19888,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="W85" s="12"/>
+      <c r="W85" s="12">
+        <v>0</v>
+      </c>
       <c r="X85" s="10"/>
       <c r="Y85" s="12"/>
       <c r="Z85" s="12">
@@ -19370,7 +19902,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:27" ht="19.149999999999999">
+    <row r="86" spans="1:27" ht="19.5">
       <c r="A86" s="10">
         <v>8</v>
       </c>
@@ -19397,7 +19929,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="K86" s="12"/>
+      <c r="K86" s="12">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
       <c r="L86" s="10"/>
       <c r="M86" s="12"/>
       <c r="N86" s="12">
@@ -19412,7 +19947,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="Q86" s="12"/>
+      <c r="Q86" s="12">
+        <v>0</v>
+      </c>
       <c r="R86" s="10"/>
       <c r="S86" s="12"/>
       <c r="T86" s="12">
@@ -19427,7 +19964,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="W86" s="12"/>
+      <c r="W86" s="12">
+        <v>0</v>
+      </c>
       <c r="X86" s="10"/>
       <c r="Y86" s="12"/>
       <c r="Z86" s="12">
@@ -19439,7 +19978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:27" ht="19.149999999999999">
+    <row r="87" spans="1:27" ht="19.5">
       <c r="A87" s="10">
         <v>8</v>
       </c>
@@ -19466,7 +20005,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="K87" s="12"/>
+      <c r="K87" s="12">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
       <c r="L87" s="10"/>
       <c r="M87" s="12"/>
       <c r="N87" s="12">
@@ -19481,7 +20023,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="Q87" s="12"/>
+      <c r="Q87" s="12">
+        <v>0</v>
+      </c>
       <c r="R87" s="10"/>
       <c r="S87" s="12"/>
       <c r="T87" s="12">
@@ -19496,7 +20040,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="W87" s="12"/>
+      <c r="W87" s="12">
+        <v>0</v>
+      </c>
       <c r="X87" s="10"/>
       <c r="Y87" s="12"/>
       <c r="Z87" s="12">
@@ -19508,7 +20054,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:27" ht="19.149999999999999">
+    <row r="88" spans="1:27" ht="19.5">
       <c r="A88" s="38">
         <v>8</v>
       </c>
@@ -19535,7 +20081,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="K88" s="12"/>
+      <c r="K88" s="12">
+        <f>IF((G88-F88)&lt;0,0,(G88-F88))</f>
+        <v>0</v>
+      </c>
       <c r="L88" s="10"/>
       <c r="M88" s="12"/>
       <c r="N88" s="12">
@@ -19550,7 +20099,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="Q88" s="12"/>
+      <c r="Q88" s="12">
+        <v>0</v>
+      </c>
       <c r="R88" s="10"/>
       <c r="S88" s="12"/>
       <c r="T88" s="12">
@@ -19565,7 +20116,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="W88" s="12"/>
+      <c r="W88" s="12">
+        <v>0</v>
+      </c>
       <c r="X88" s="10"/>
       <c r="Y88" s="12"/>
       <c r="Z88" s="12">
@@ -19577,7 +20130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:27" ht="19.149999999999999">
+    <row r="89" spans="1:27" ht="19.5">
       <c r="A89" s="10">
         <v>8</v>
       </c>
@@ -19604,7 +20157,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="K89" s="12"/>
+      <c r="K89" s="12">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
       <c r="L89" s="10"/>
       <c r="M89" s="12"/>
       <c r="N89" s="12">
@@ -19619,7 +20175,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="Q89" s="12"/>
+      <c r="Q89" s="12">
+        <v>0</v>
+      </c>
       <c r="R89" s="10"/>
       <c r="S89" s="12"/>
       <c r="T89" s="12">
@@ -19634,7 +20192,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="W89" s="12"/>
+      <c r="W89" s="12">
+        <v>0</v>
+      </c>
       <c r="X89" s="10"/>
       <c r="Y89" s="12"/>
       <c r="Z89" s="12">
@@ -19647,7 +20207,7 @@
       </c>
     </row>
     <row r="90" spans="1:27" s="7" customFormat="1"/>
-    <row r="91" spans="1:27" ht="19.149999999999999">
+    <row r="91" spans="1:27" ht="19.5">
       <c r="A91" s="10">
         <v>9</v>
       </c>
@@ -19674,7 +20234,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="K91" s="12"/>
+      <c r="K91" s="12">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
       <c r="L91" s="10"/>
       <c r="M91" s="12"/>
       <c r="N91" s="12">
@@ -19689,7 +20252,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="Q91" s="12"/>
+      <c r="Q91" s="12">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
       <c r="R91" s="10"/>
       <c r="S91" s="12"/>
       <c r="T91" s="12">
@@ -19704,7 +20270,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="W91" s="12"/>
+      <c r="W91" s="12">
+        <v>0</v>
+      </c>
       <c r="X91" s="10"/>
       <c r="Y91" s="12"/>
       <c r="Z91" s="12">
@@ -19716,7 +20284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:27" ht="19.149999999999999">
+    <row r="92" spans="1:27" ht="19.5">
       <c r="A92" s="10">
         <v>9</v>
       </c>
@@ -19743,7 +20311,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="K92" s="12"/>
+      <c r="K92" s="12">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
       <c r="L92" s="10"/>
       <c r="M92" s="12"/>
       <c r="N92" s="12">
@@ -19758,7 +20329,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="Q92" s="12"/>
+      <c r="Q92" s="12">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
       <c r="R92" s="10"/>
       <c r="S92" s="12"/>
       <c r="T92" s="12">
@@ -19773,7 +20347,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="W92" s="12"/>
+      <c r="W92" s="12">
+        <v>0</v>
+      </c>
       <c r="X92" s="10"/>
       <c r="Y92" s="12"/>
       <c r="Z92" s="12">
@@ -19785,7 +20361,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:27" ht="19.149999999999999">
+    <row r="93" spans="1:27" ht="19.5">
       <c r="A93" s="10">
         <v>9</v>
       </c>
@@ -19812,7 +20388,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="K93" s="12"/>
+      <c r="K93" s="12">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
       <c r="L93" s="10"/>
       <c r="M93" s="12"/>
       <c r="N93" s="12">
@@ -19827,7 +20406,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="Q93" s="12"/>
+      <c r="Q93" s="12">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
       <c r="R93" s="10"/>
       <c r="S93" s="12"/>
       <c r="T93" s="12">
@@ -19842,7 +20424,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="W93" s="12"/>
+      <c r="W93" s="12">
+        <v>0</v>
+      </c>
       <c r="X93" s="10"/>
       <c r="Y93" s="12"/>
       <c r="Z93" s="12">
@@ -19854,7 +20438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:27" ht="19.149999999999999">
+    <row r="94" spans="1:27" ht="19.5">
       <c r="A94" s="10">
         <v>9</v>
       </c>
@@ -19881,7 +20465,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="K94" s="12"/>
+      <c r="K94" s="12">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
       <c r="L94" s="10"/>
       <c r="M94" s="12"/>
       <c r="N94" s="12">
@@ -19896,7 +20483,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="Q94" s="12"/>
+      <c r="Q94" s="12">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
       <c r="R94" s="10"/>
       <c r="S94" s="12"/>
       <c r="T94" s="12">
@@ -19911,7 +20501,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="W94" s="12"/>
+      <c r="W94" s="12">
+        <v>0</v>
+      </c>
       <c r="X94" s="10"/>
       <c r="Y94" s="12"/>
       <c r="Z94" s="12">
@@ -19923,7 +20515,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:27" ht="19.149999999999999">
+    <row r="95" spans="1:27" ht="19.5">
       <c r="A95" s="10">
         <v>9</v>
       </c>
@@ -19950,7 +20542,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="K95" s="12"/>
+      <c r="K95" s="12">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
       <c r="L95" s="10"/>
       <c r="M95" s="12"/>
       <c r="N95" s="12">
@@ -19965,7 +20560,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="Q95" s="12"/>
+      <c r="Q95" s="12">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
       <c r="R95" s="10"/>
       <c r="S95" s="12"/>
       <c r="T95" s="12">
@@ -19980,7 +20578,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="W95" s="12"/>
+      <c r="W95" s="12">
+        <v>0</v>
+      </c>
       <c r="X95" s="10"/>
       <c r="Y95" s="12"/>
       <c r="Z95" s="12">
@@ -19992,7 +20592,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:27" ht="19.149999999999999">
+    <row r="96" spans="1:27" ht="19.5">
       <c r="A96" s="10">
         <v>9</v>
       </c>
@@ -20019,7 +20619,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="K96" s="12"/>
+      <c r="K96" s="12">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
       <c r="L96" s="10"/>
       <c r="M96" s="12"/>
       <c r="N96" s="12">
@@ -20034,7 +20637,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="Q96" s="12"/>
+      <c r="Q96" s="12">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
       <c r="R96" s="10"/>
       <c r="S96" s="12"/>
       <c r="T96" s="12">
@@ -20049,7 +20655,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="W96" s="12"/>
+      <c r="W96" s="12">
+        <v>0</v>
+      </c>
       <c r="X96" s="10"/>
       <c r="Y96" s="12"/>
       <c r="Z96" s="12">
@@ -20061,7 +20669,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:27" ht="19.149999999999999">
+    <row r="97" spans="1:27" ht="19.5">
       <c r="A97" s="38">
         <v>9</v>
       </c>
@@ -20088,7 +20696,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="K97" s="12"/>
+      <c r="K97" s="12">
+        <f>IF((G97-F97)&lt;0,0,(G97-F97))</f>
+        <v>0</v>
+      </c>
       <c r="L97" s="10"/>
       <c r="M97" s="12"/>
       <c r="N97" s="12">
@@ -20103,7 +20714,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="Q97" s="12"/>
+      <c r="Q97" s="12">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
       <c r="R97" s="10"/>
       <c r="S97" s="12"/>
       <c r="T97" s="12">
@@ -20118,7 +20732,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="W97" s="12"/>
+      <c r="W97" s="12">
+        <v>0</v>
+      </c>
       <c r="X97" s="10"/>
       <c r="Y97" s="12"/>
       <c r="Z97" s="12">
@@ -20130,7 +20746,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:27" ht="19.149999999999999">
+    <row r="98" spans="1:27" ht="19.5">
       <c r="A98" s="10">
         <v>9</v>
       </c>
@@ -20157,7 +20773,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="K98" s="12"/>
+      <c r="K98" s="12">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
       <c r="L98" s="10"/>
       <c r="M98" s="12"/>
       <c r="N98" s="12">
@@ -20172,7 +20791,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="Q98" s="12"/>
+      <c r="Q98" s="12">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
       <c r="R98" s="10"/>
       <c r="S98" s="12"/>
       <c r="T98" s="12">
@@ -20187,7 +20809,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="W98" s="12"/>
+      <c r="W98" s="12">
+        <v>0</v>
+      </c>
       <c r="X98" s="10"/>
       <c r="Y98" s="12"/>
       <c r="Z98" s="12">
@@ -20199,7 +20823,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:27" ht="19.149999999999999">
+    <row r="99" spans="1:27" ht="19.5">
       <c r="A99" s="10">
         <v>9</v>
       </c>
@@ -20226,7 +20850,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="K99" s="12"/>
+      <c r="K99" s="12">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
       <c r="L99" s="10"/>
       <c r="M99" s="12"/>
       <c r="N99" s="12">
@@ -20241,7 +20868,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="Q99" s="12"/>
+      <c r="Q99" s="12">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
       <c r="R99" s="10"/>
       <c r="S99" s="12"/>
       <c r="T99" s="12">
@@ -20256,7 +20886,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="W99" s="12"/>
+      <c r="W99" s="12">
+        <v>0</v>
+      </c>
       <c r="X99" s="10"/>
       <c r="Y99" s="12"/>
       <c r="Z99" s="12">
@@ -20268,7 +20900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:27" ht="19.149999999999999">
+    <row r="100" spans="1:27" ht="19.5">
       <c r="A100" s="38">
         <v>9</v>
       </c>
@@ -20295,7 +20927,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="K100" s="12"/>
+      <c r="K100" s="12">
+        <f>IF((G100-F100)&lt;0,0,(G100-F100))</f>
+        <v>0</v>
+      </c>
       <c r="L100" s="10"/>
       <c r="M100" s="12"/>
       <c r="N100" s="12">
@@ -20310,7 +20945,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="Q100" s="12"/>
+      <c r="Q100" s="12">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
       <c r="R100" s="10"/>
       <c r="S100" s="12"/>
       <c r="T100" s="12">
@@ -20325,7 +20963,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="W100" s="12"/>
+      <c r="W100" s="12">
+        <v>0</v>
+      </c>
       <c r="X100" s="10"/>
       <c r="Y100" s="12"/>
       <c r="Z100" s="12">
@@ -20337,7 +20977,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:27" ht="19.149999999999999">
+    <row r="101" spans="1:27" ht="19.5">
       <c r="A101" s="10">
         <v>9</v>
       </c>
@@ -20364,7 +21004,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="K101" s="12"/>
+      <c r="K101" s="12">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
       <c r="L101" s="10"/>
       <c r="M101" s="12"/>
       <c r="N101" s="12">
@@ -20379,7 +21022,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="Q101" s="12"/>
+      <c r="Q101" s="12">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
       <c r="R101" s="10"/>
       <c r="S101" s="12"/>
       <c r="T101" s="12">
@@ -20394,7 +21040,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="W101" s="12"/>
+      <c r="W101" s="12">
+        <v>0</v>
+      </c>
       <c r="X101" s="10"/>
       <c r="Y101" s="12"/>
       <c r="Z101" s="12">
@@ -20407,7 +21055,7 @@
       </c>
     </row>
     <row r="102" spans="1:27" s="7" customFormat="1"/>
-    <row r="103" spans="1:27" ht="19.149999999999999">
+    <row r="103" spans="1:27" ht="19.5">
       <c r="A103" s="10">
         <v>10</v>
       </c>
@@ -20434,7 +21082,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="K103" s="12"/>
+      <c r="K103" s="12">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
       <c r="L103" s="10"/>
       <c r="M103" s="12"/>
       <c r="N103" s="12">
@@ -20449,7 +21100,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="Q103" s="12"/>
+      <c r="Q103" s="12">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
       <c r="R103" s="10"/>
       <c r="S103" s="12"/>
       <c r="T103" s="12">
@@ -20464,7 +21118,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="W103" s="12"/>
+      <c r="W103" s="12">
+        <v>0</v>
+      </c>
       <c r="X103" s="10"/>
       <c r="Y103" s="12"/>
       <c r="Z103" s="12">
@@ -20476,7 +21132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:27" ht="19.149999999999999">
+    <row r="104" spans="1:27" ht="19.5">
       <c r="A104" s="10">
         <v>10</v>
       </c>
@@ -20503,7 +21159,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="K104" s="12"/>
+      <c r="K104" s="12">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
       <c r="L104" s="10"/>
       <c r="M104" s="12"/>
       <c r="N104" s="12">
@@ -20518,7 +21177,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="Q104" s="12"/>
+      <c r="Q104" s="12">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
       <c r="R104" s="10"/>
       <c r="S104" s="12"/>
       <c r="T104" s="12">
@@ -20533,7 +21195,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="W104" s="12"/>
+      <c r="W104" s="12">
+        <v>0</v>
+      </c>
       <c r="X104" s="10"/>
       <c r="Y104" s="12"/>
       <c r="Z104" s="12">
@@ -20545,7 +21209,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:27" ht="19.149999999999999">
+    <row r="105" spans="1:27" ht="19.5">
       <c r="A105" s="10">
         <v>10</v>
       </c>
@@ -20572,7 +21236,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="K105" s="12"/>
+      <c r="K105" s="12">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
       <c r="L105" s="10"/>
       <c r="M105" s="12"/>
       <c r="N105" s="12">
@@ -20587,7 +21254,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="Q105" s="12"/>
+      <c r="Q105" s="12">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
       <c r="R105" s="10"/>
       <c r="S105" s="12"/>
       <c r="T105" s="12">
@@ -20602,7 +21272,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="W105" s="12"/>
+      <c r="W105" s="12">
+        <v>0</v>
+      </c>
       <c r="X105" s="10"/>
       <c r="Y105" s="12"/>
       <c r="Z105" s="12">
@@ -20614,7 +21286,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:27" ht="19.149999999999999">
+    <row r="106" spans="1:27" ht="19.5">
       <c r="A106" s="10">
         <v>10</v>
       </c>
@@ -20641,7 +21313,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="K106" s="12"/>
+      <c r="K106" s="12">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
       <c r="L106" s="10"/>
       <c r="M106" s="12"/>
       <c r="N106" s="12">
@@ -20656,7 +21331,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="Q106" s="12"/>
+      <c r="Q106" s="12">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
       <c r="R106" s="10"/>
       <c r="S106" s="12"/>
       <c r="T106" s="12">
@@ -20671,7 +21349,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="W106" s="12"/>
+      <c r="W106" s="12">
+        <v>0</v>
+      </c>
       <c r="X106" s="10"/>
       <c r="Y106" s="12"/>
       <c r="Z106" s="12">
@@ -20683,7 +21363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:27" ht="19.149999999999999">
+    <row r="107" spans="1:27" ht="19.5">
       <c r="A107" s="10">
         <v>10</v>
       </c>
@@ -20710,7 +21390,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="K107" s="12"/>
+      <c r="K107" s="12">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
       <c r="L107" s="10"/>
       <c r="M107" s="12"/>
       <c r="N107" s="12">
@@ -20725,7 +21408,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="Q107" s="12"/>
+      <c r="Q107" s="12">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
       <c r="R107" s="10"/>
       <c r="S107" s="12"/>
       <c r="T107" s="12">
@@ -20740,7 +21426,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="W107" s="12"/>
+      <c r="W107" s="12">
+        <v>0</v>
+      </c>
       <c r="X107" s="10"/>
       <c r="Y107" s="12"/>
       <c r="Z107" s="12">
@@ -20752,7 +21440,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:27" ht="19.149999999999999">
+    <row r="108" spans="1:27" ht="19.5">
       <c r="A108" s="10">
         <v>10</v>
       </c>
@@ -20779,7 +21467,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="K108" s="12"/>
+      <c r="K108" s="12">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
       <c r="L108" s="10"/>
       <c r="M108" s="12"/>
       <c r="N108" s="12">
@@ -20794,7 +21485,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="Q108" s="12"/>
+      <c r="Q108" s="12">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
       <c r="R108" s="10"/>
       <c r="S108" s="12"/>
       <c r="T108" s="12">
@@ -20809,7 +21503,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="W108" s="12"/>
+      <c r="W108" s="12">
+        <v>0</v>
+      </c>
       <c r="X108" s="10"/>
       <c r="Y108" s="12"/>
       <c r="Z108" s="12">
@@ -20821,7 +21517,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:27" ht="19.149999999999999">
+    <row r="109" spans="1:27" ht="19.5">
       <c r="A109" s="38">
         <v>10</v>
       </c>
@@ -20848,7 +21544,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="K109" s="12"/>
+      <c r="K109" s="12">
+        <f>IF((G109-F109)&lt;0,0,(G109-F109))</f>
+        <v>0</v>
+      </c>
       <c r="L109" s="10"/>
       <c r="M109" s="12"/>
       <c r="N109" s="12">
@@ -20863,7 +21562,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="Q109" s="12"/>
+      <c r="Q109" s="12">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
       <c r="R109" s="10"/>
       <c r="S109" s="12"/>
       <c r="T109" s="12">
@@ -20878,7 +21580,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="W109" s="12"/>
+      <c r="W109" s="12">
+        <v>0</v>
+      </c>
       <c r="X109" s="10"/>
       <c r="Y109" s="12"/>
       <c r="Z109" s="12">
@@ -20890,7 +21594,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:27" ht="19.149999999999999">
+    <row r="110" spans="1:27" ht="19.5">
       <c r="A110" s="10">
         <v>10</v>
       </c>
@@ -20917,7 +21621,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="K110" s="12"/>
+      <c r="K110" s="12">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
       <c r="L110" s="10"/>
       <c r="M110" s="12"/>
       <c r="N110" s="12">
@@ -20932,7 +21639,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="Q110" s="12"/>
+      <c r="Q110" s="12">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
       <c r="R110" s="10"/>
       <c r="S110" s="12"/>
       <c r="T110" s="12">
@@ -20947,7 +21657,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="W110" s="12"/>
+      <c r="W110" s="12">
+        <v>0</v>
+      </c>
       <c r="X110" s="10"/>
       <c r="Y110" s="12"/>
       <c r="Z110" s="12">
@@ -20959,7 +21671,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:27" ht="19.149999999999999">
+    <row r="111" spans="1:27" ht="19.5">
       <c r="A111" s="10">
         <v>10</v>
       </c>
@@ -20986,7 +21698,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="K111" s="12"/>
+      <c r="K111" s="12">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
       <c r="L111" s="10"/>
       <c r="M111" s="12"/>
       <c r="N111" s="12">
@@ -21001,7 +21716,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="Q111" s="12"/>
+      <c r="Q111" s="12">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
       <c r="R111" s="10"/>
       <c r="S111" s="12"/>
       <c r="T111" s="12">
@@ -21016,7 +21734,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="W111" s="12"/>
+      <c r="W111" s="12">
+        <v>0</v>
+      </c>
       <c r="X111" s="10"/>
       <c r="Y111" s="12"/>
       <c r="Z111" s="12">
@@ -21028,7 +21748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:27" ht="19.149999999999999">
+    <row r="112" spans="1:27" ht="19.5">
       <c r="A112" s="38">
         <v>10</v>
       </c>
@@ -21055,7 +21775,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="K112" s="12"/>
+      <c r="K112" s="12">
+        <f>IF((G112-F112)&lt;0,0,(G112-F112))</f>
+        <v>0</v>
+      </c>
       <c r="L112" s="10"/>
       <c r="M112" s="12"/>
       <c r="N112" s="12">
@@ -21070,7 +21793,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="Q112" s="12"/>
+      <c r="Q112" s="12">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
       <c r="R112" s="10"/>
       <c r="S112" s="12"/>
       <c r="T112" s="12">
@@ -21085,7 +21811,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="W112" s="12"/>
+      <c r="W112" s="12">
+        <v>0</v>
+      </c>
       <c r="X112" s="10"/>
       <c r="Y112" s="12"/>
       <c r="Z112" s="12">
@@ -21097,7 +21825,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:28" ht="19.149999999999999">
+    <row r="113" spans="1:28" ht="19.5">
       <c r="A113" s="10">
         <v>10</v>
       </c>
@@ -21124,7 +21852,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="K113" s="12"/>
+      <c r="K113" s="12">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
       <c r="L113" s="10"/>
       <c r="M113" s="12"/>
       <c r="N113" s="12">
@@ -21139,7 +21870,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="Q113" s="12"/>
+      <c r="Q113" s="12">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
       <c r="R113" s="10"/>
       <c r="S113" s="12"/>
       <c r="T113" s="12">
@@ -21154,7 +21888,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="W113" s="12"/>
+      <c r="W113" s="12">
+        <v>0</v>
+      </c>
       <c r="X113" s="10"/>
       <c r="Y113" s="12"/>
       <c r="Z113" s="12">
@@ -21167,7 +21903,7 @@
       </c>
     </row>
     <row r="114" spans="1:28" s="7" customFormat="1"/>
-    <row r="115" spans="1:28" ht="38.450000000000003">
+    <row r="115" spans="1:28" ht="38.25">
       <c r="A115" s="1" t="s">
         <v>26</v>
       </c>
@@ -21194,7 +21930,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="K115" s="5"/>
+      <c r="K115" s="5">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
       <c r="L115" s="1"/>
       <c r="M115" s="5"/>
       <c r="N115" s="5">
@@ -21209,7 +21948,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="Q115" s="5"/>
+      <c r="Q115" s="5">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
       <c r="R115" s="1"/>
       <c r="S115" s="5"/>
       <c r="T115" s="5">
@@ -21224,7 +21966,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="W115" s="5"/>
+      <c r="W115" s="5">
+        <v>0</v>
+      </c>
       <c r="X115" s="1"/>
       <c r="Y115" s="5"/>
       <c r="Z115" s="5">
@@ -21236,7 +21980,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:28" ht="19.149999999999999">
+    <row r="116" spans="1:28" ht="19.5">
       <c r="A116" s="1" t="s">
         <v>26</v>
       </c>
@@ -21263,7 +22007,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="K116" s="5"/>
+      <c r="K116" s="5">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
       <c r="L116" s="1"/>
       <c r="M116" s="5"/>
       <c r="N116" s="5">
@@ -21278,7 +22025,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="Q116" s="5"/>
+      <c r="Q116" s="5">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
       <c r="R116" s="1"/>
       <c r="S116" s="5"/>
       <c r="T116" s="5">
@@ -21293,7 +22043,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="W116" s="5"/>
+      <c r="W116" s="5">
+        <v>0</v>
+      </c>
       <c r="X116" s="1"/>
       <c r="Y116" s="5"/>
       <c r="Z116" s="5">
@@ -21305,7 +22057,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:28" ht="19.149999999999999">
+    <row r="117" spans="1:28" ht="19.5">
       <c r="A117" s="1" t="s">
         <v>26</v>
       </c>
@@ -21332,7 +22084,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="K117" s="5"/>
+      <c r="K117" s="5">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
       <c r="L117" s="1"/>
       <c r="M117" s="5"/>
       <c r="N117" s="5">
@@ -21347,7 +22102,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="Q117" s="5"/>
+      <c r="Q117" s="5">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
       <c r="R117" s="1"/>
       <c r="S117" s="5"/>
       <c r="T117" s="5">
@@ -21362,7 +22120,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="W117" s="5"/>
+      <c r="W117" s="5">
+        <v>0</v>
+      </c>
       <c r="X117" s="1"/>
       <c r="Y117" s="5"/>
       <c r="Z117" s="5">
@@ -21374,7 +22134,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:28" ht="19.149999999999999">
+    <row r="118" spans="1:28" ht="19.5">
       <c r="A118" s="1" t="s">
         <v>26</v>
       </c>
@@ -21401,7 +22161,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="K118" s="5"/>
+      <c r="K118" s="5">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
       <c r="L118" s="1"/>
       <c r="M118" s="5"/>
       <c r="N118" s="5">
@@ -21416,7 +22179,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="Q118" s="5"/>
+      <c r="Q118" s="5">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
       <c r="R118" s="1"/>
       <c r="S118" s="5"/>
       <c r="T118" s="5">
@@ -21431,7 +22197,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="W118" s="5"/>
+      <c r="W118" s="5">
+        <v>0</v>
+      </c>
       <c r="X118" s="1"/>
       <c r="Y118" s="5"/>
       <c r="Z118" s="5">
@@ -21443,7 +22211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:28" ht="38.450000000000003">
+    <row r="119" spans="1:28" ht="38.25">
       <c r="A119" s="1" t="s">
         <v>26</v>
       </c>
@@ -21470,7 +22238,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="K119" s="5"/>
+      <c r="K119" s="5">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
       <c r="L119" s="1"/>
       <c r="M119" s="5"/>
       <c r="N119" s="5">
@@ -21485,7 +22256,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="Q119" s="5"/>
+      <c r="Q119" s="5">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
       <c r="R119" s="1"/>
       <c r="S119" s="5"/>
       <c r="T119" s="5">
@@ -21500,7 +22274,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="W119" s="5"/>
+      <c r="W119" s="5">
+        <v>0</v>
+      </c>
       <c r="X119" s="1"/>
       <c r="Y119" s="5"/>
       <c r="Z119" s="5">
@@ -21512,7 +22288,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:28" ht="19.149999999999999">
+    <row r="120" spans="1:28" ht="38.25">
       <c r="A120" s="1" t="s">
         <v>26</v>
       </c>
@@ -21539,7 +22315,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="K120" s="5"/>
+      <c r="K120" s="5">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
       <c r="L120" s="1"/>
       <c r="M120" s="5"/>
       <c r="N120" s="5">
@@ -21554,7 +22333,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="Q120" s="5"/>
+      <c r="Q120" s="5">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
       <c r="R120" s="1"/>
       <c r="S120" s="5"/>
       <c r="T120" s="5">
@@ -21569,7 +22351,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="W120" s="5"/>
+      <c r="W120" s="5">
+        <v>0</v>
+      </c>
       <c r="X120" s="1"/>
       <c r="Y120" s="5"/>
       <c r="Z120" s="5">
@@ -21581,7 +22365,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:28" ht="38.450000000000003">
+    <row r="121" spans="1:28" ht="57.75">
       <c r="A121" s="1" t="s">
         <v>26</v>
       </c>
@@ -21608,7 +22392,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="K121" s="5"/>
+      <c r="K121" s="5">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
       <c r="L121" s="1"/>
       <c r="M121" s="5"/>
       <c r="N121" s="5">
@@ -21623,7 +22410,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="Q121" s="5"/>
+      <c r="Q121" s="5">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
       <c r="R121" s="1"/>
       <c r="S121" s="5"/>
       <c r="T121" s="5">
@@ -21638,7 +22428,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="W121" s="5"/>
+      <c r="W121" s="5">
+        <v>0</v>
+      </c>
       <c r="X121" s="1"/>
       <c r="Y121" s="5"/>
       <c r="Z121" s="5">
@@ -21650,7 +22442,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:28" ht="38.450000000000003">
+    <row r="122" spans="1:28" ht="38.25">
       <c r="A122" s="1" t="s">
         <v>26</v>
       </c>
@@ -21677,7 +22469,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="K122" s="5"/>
+      <c r="K122" s="5">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
       <c r="L122" s="1"/>
       <c r="M122" s="5"/>
       <c r="N122" s="5">
@@ -21692,7 +22487,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="Q122" s="5"/>
+      <c r="Q122" s="5">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
       <c r="R122" s="1"/>
       <c r="S122" s="5"/>
       <c r="T122" s="5">
@@ -21707,7 +22505,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="W122" s="5"/>
+      <c r="W122" s="5">
+        <v>0</v>
+      </c>
       <c r="X122" s="1"/>
       <c r="Y122" s="5"/>
       <c r="Z122" s="5">
@@ -22413,7 +23213,7 @@
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C67:C77 C79:C89 C115:C122 C103:C113 C91:C101 C2:C10 C12:C19 C21:C29 C31:C41 C43:C53 C55:C65" name="Textbooks"/>
-    <protectedRange sqref="J2:L2 D2:F10 D12:F19 D21:F29 D31:F41 D43:F53 D55:F65 D67:F77 D79:F89 D91:F101 D115:F122 P2:R10 N3:O10 V2:X10 T3:U10 N12:R19 T12:X19 H3:L10 Z3:AA10 Z12:AA19 H12:L19 N21:R29 T21:X29 Z21:AA29 H21:L29 T31:X41 Z31:AA41 H31:L41 T43:X53 Z43:AA53 H43:L53 T55:X65 Z55:AA65 H55:L65 T67:X77 Z67:AA77 H67:L77 T79:X89 Z79:AA89 H79:L89 T91:X101 Z91:AA101 H91:L101 T103:X113 Z103:AA113 H103:L113 N115:R122 T115:X122 Z115:AA122 H115:L122 D103:F113 N31:R41 N43:R53 N55:R65 N67:R77 N79:R89 N91:R101 N103:R113" name="LAS"/>
+    <protectedRange sqref="J2:L2 D2:F10 D12:F19 D21:F29 D31:F41 D43:F53 D55:F65 D67:F77 D79:F89 D91:F101 D115:F122 P2:R10 N3:O10 V2:X10 T3:U10 N12:R19 T12:X19 Z3:AA10 Z12:AA19 N21:R29 T21:X29 Z21:AA29 T31:X41 Z31:AA41 T43:X53 Z43:AA53 T55:X65 Z55:AA65 T67:X77 Z67:AA77 T79:X89 Z79:AA89 T91:X101 Z91:AA101 T103:X113 Z103:AA113 T115:X122 Z115:AA122 D103:F113 N31:R41 N43:R53 N55:R65 N67:R77 N79:R89 N115:R122 N91:R101 N103:R113 H3:L10 H12:L19 H21:L29 H31:L41 H43:L53 H55:L65 H67:L77 H79:L89 H91:L101 H103:L113 H115:L122" name="LAS"/>
     <protectedRange sqref="G2:I2 M2:O2 S2:U2 Y2:AA2 G3:G10 M3:M10 S3:S10 Y3:Y10 Y12:Y19 G12:G19 M12:M19 S12:S19 Y21:Y29 G21:G29 M21:M29 S21:S29 Y31:Y41 G31:G41 M31:M41 S31:S41 Y43:Y53 G43:G53 M43:M53 S43:S53 Y55:Y65 G55:G65 M55:M65 S55:S65 Y67:Y77 G67:G77 M67:M77 S67:S77 Y79:Y89 G79:G89 M79:M89 S79:S89 Y91:Y101 G91:G101 M91:M101 S91:S101 Y103:Y113 G103:G113 M103:M113 S103:S113 Y115:Y122 G115:G122 M115:M122 S115:S122" name="SOURCE"/>
   </protectedRanges>
   <dataConsolidate/>
